--- a/outputs/trades_000001_双均线策略.xlsx
+++ b/outputs/trades_000001_双均线策略.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
         <v>43881</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1139</v>
+        <v>13.1126</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>43893</v>
@@ -501,16 +501,16 @@
         <v>43892</v>
       </c>
       <c r="F2" t="n">
-        <v>12.2463</v>
+        <v>12.2476</v>
       </c>
       <c r="G2" t="n">
         <v>7623</v>
       </c>
       <c r="H2" t="n">
-        <v>-6671.7722</v>
+        <v>-6652.44</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06673900000000001</v>
+        <v>-0.066553</v>
       </c>
       <c r="J2" t="n">
         <v>11</v>
@@ -524,7 +524,7 @@
         <v>43936</v>
       </c>
       <c r="C3" t="n">
-        <v>10.2131</v>
+        <v>10.212</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>43941</v>
@@ -533,16 +533,16 @@
         <v>43938</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5168</v>
+        <v>10.5179</v>
       </c>
       <c r="G3" t="n">
-        <v>9135</v>
+        <v>9138</v>
       </c>
       <c r="H3" t="n">
-        <v>2718.2291</v>
+        <v>2738.0648</v>
       </c>
       <c r="I3" t="n">
-        <v>0.029135</v>
+        <v>0.029341</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
@@ -556,7 +556,7 @@
         <v>43941</v>
       </c>
       <c r="C4" t="n">
-        <v>10.9833</v>
+        <v>10.9822</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>43970</v>
@@ -565,16 +565,16 @@
         <v>43969</v>
       </c>
       <c r="F4" t="n">
-        <v>10.8867</v>
+        <v>10.8878</v>
       </c>
       <c r="G4" t="n">
-        <v>8742</v>
+        <v>8746</v>
       </c>
       <c r="H4" t="n">
-        <v>-901.4926</v>
+        <v>-882.7776</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.009389</v>
+        <v>-0.009191</v>
       </c>
       <c r="J4" t="n">
         <v>28</v>
@@ -588,7 +588,7 @@
         <v>43985</v>
       </c>
       <c r="C5" t="n">
-        <v>11.3134</v>
+        <v>11.3123</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>43999</v>
@@ -597,16 +597,16 @@
         <v>43998</v>
       </c>
       <c r="F5" t="n">
-        <v>10.5868</v>
+        <v>10.5879</v>
       </c>
       <c r="G5" t="n">
-        <v>8407</v>
+        <v>8413</v>
       </c>
       <c r="H5" t="n">
-        <v>-6163.5085</v>
+        <v>-6149.4827</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.064803</v>
+        <v>-0.06461600000000001</v>
       </c>
       <c r="J5" t="n">
         <v>13</v>
@@ -620,7 +620,7 @@
         <v>44015</v>
       </c>
       <c r="C6" t="n">
-        <v>13.424</v>
+        <v>13.4227</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>44039</v>
@@ -629,16 +629,16 @@
         <v>44036</v>
       </c>
       <c r="F6" t="n">
-        <v>10.9767</v>
+        <v>10.9778</v>
       </c>
       <c r="G6" t="n">
-        <v>6626</v>
+        <v>6632</v>
       </c>
       <c r="H6" t="n">
-        <v>-16264.4461</v>
+        <v>-16262.9914</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.182854</v>
+        <v>-0.182691</v>
       </c>
       <c r="J6" t="n">
         <v>21</v>
@@ -652,7 +652,7 @@
         <v>44054</v>
       </c>
       <c r="C7" t="n">
-        <v>12.1236</v>
+        <v>12.1224</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>44104</v>
@@ -661,16 +661,16 @@
         <v>44103</v>
       </c>
       <c r="F7" t="n">
-        <v>12.9061</v>
+        <v>12.9074</v>
       </c>
       <c r="G7" t="n">
-        <v>5996</v>
+        <v>6002</v>
       </c>
       <c r="H7" t="n">
-        <v>4646.7925</v>
+        <v>4666.4653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06392299999999999</v>
+        <v>0.064136</v>
       </c>
       <c r="J7" t="n">
         <v>49</v>
@@ -684,7 +684,7 @@
         <v>44118</v>
       </c>
       <c r="C8" t="n">
-        <v>14.3043</v>
+        <v>14.3029</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>44151</v>
@@ -693,16 +693,16 @@
         <v>44148</v>
       </c>
       <c r="F8" t="n">
-        <v>15.1055</v>
+        <v>15.107</v>
       </c>
       <c r="G8" t="n">
-        <v>5406</v>
+        <v>5413</v>
       </c>
       <c r="H8" t="n">
-        <v>4283.4661</v>
+        <v>4304.9321</v>
       </c>
       <c r="I8" t="n">
-        <v>0.055393</v>
+        <v>0.055604</v>
       </c>
       <c r="J8" t="n">
         <v>32</v>
@@ -716,7 +716,7 @@
         <v>44154</v>
       </c>
       <c r="C9" t="n">
-        <v>16.605</v>
+        <v>16.6033</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>44176</v>
@@ -725,16 +725,16 @@
         <v>44175</v>
       </c>
       <c r="F9" t="n">
-        <v>16.2551</v>
+        <v>16.2567</v>
       </c>
       <c r="G9" t="n">
-        <v>4915</v>
+        <v>4922</v>
       </c>
       <c r="H9" t="n">
-        <v>-1768.0043</v>
+        <v>-1754.3486</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.021663</v>
+        <v>-0.021467</v>
       </c>
       <c r="J9" t="n">
         <v>21</v>
@@ -748,7 +748,7 @@
         <v>44195</v>
       </c>
       <c r="C10" t="n">
-        <v>17.0851</v>
+        <v>17.0834</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>44251</v>
@@ -757,16 +757,16 @@
         <v>44250</v>
       </c>
       <c r="F10" t="n">
-        <v>19.894</v>
+        <v>19.896</v>
       </c>
       <c r="G10" t="n">
-        <v>4673</v>
+        <v>4681</v>
       </c>
       <c r="H10" t="n">
-        <v>13074.1767</v>
+        <v>13113.8691</v>
       </c>
       <c r="I10" t="n">
-        <v>0.163757</v>
+        <v>0.16399</v>
       </c>
       <c r="J10" t="n">
         <v>55</v>
@@ -780,7 +780,7 @@
         <v>44286</v>
       </c>
       <c r="C11" t="n">
-        <v>19.5259</v>
+        <v>19.5239</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>44300</v>
@@ -789,16 +789,16 @@
         <v>44299</v>
       </c>
       <c r="F11" t="n">
-        <v>18.4045</v>
+        <v>18.4063</v>
       </c>
       <c r="G11" t="n">
-        <v>4759</v>
+        <v>4768</v>
       </c>
       <c r="H11" t="n">
-        <v>-5390.7958</v>
+        <v>-5382.9054</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.058013</v>
+        <v>-0.057825</v>
       </c>
       <c r="J11" t="n">
         <v>13</v>
@@ -812,7 +812,7 @@
         <v>44308</v>
       </c>
       <c r="C12" t="n">
-        <v>21.0363</v>
+        <v>21.0342</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>44363</v>
@@ -821,16 +821,16 @@
         <v>44362</v>
       </c>
       <c r="F12" t="n">
-        <v>21.1736</v>
+        <v>21.1758</v>
       </c>
       <c r="G12" t="n">
-        <v>4161</v>
+        <v>4169</v>
       </c>
       <c r="H12" t="n">
-        <v>518.7686</v>
+        <v>537.3633</v>
       </c>
       <c r="I12" t="n">
-        <v>0.005927</v>
+        <v>0.006128</v>
       </c>
       <c r="J12" t="n">
         <v>54</v>
@@ -844,7 +844,7 @@
         <v>44420</v>
       </c>
       <c r="C13" t="n">
-        <v>17.8153</v>
+        <v>17.8136</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>44438</v>
@@ -853,16 +853,16 @@
         <v>44435</v>
       </c>
       <c r="F13" t="n">
-        <v>15.6353</v>
+        <v>15.6369</v>
       </c>
       <c r="G13" t="n">
-        <v>4942</v>
+        <v>4954</v>
       </c>
       <c r="H13" t="n">
-        <v>-10823.3269</v>
+        <v>-10833.0363</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.122932</v>
+        <v>-0.122756</v>
       </c>
       <c r="J13" t="n">
         <v>17</v>
@@ -876,7 +876,7 @@
         <v>44449</v>
       </c>
       <c r="C14" t="n">
-        <v>18.1354</v>
+        <v>18.1336</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>44463</v>
@@ -885,16 +885,16 @@
         <v>44462</v>
       </c>
       <c r="F14" t="n">
-        <v>15.2654</v>
+        <v>15.2669</v>
       </c>
       <c r="G14" t="n">
-        <v>4258</v>
+        <v>4269</v>
       </c>
       <c r="H14" t="n">
-        <v>-12263.2114</v>
+        <v>-12280.633</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.158807</v>
+        <v>-0.158639</v>
       </c>
       <c r="J14" t="n">
         <v>11</v>
@@ -908,7 +908,7 @@
         <v>44482</v>
       </c>
       <c r="C15" t="n">
-        <v>17.1351</v>
+        <v>17.1334</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>44503</v>
@@ -917,16 +917,16 @@
         <v>44502</v>
       </c>
       <c r="F15" t="n">
-        <v>15.9452</v>
+        <v>15.9468</v>
       </c>
       <c r="G15" t="n">
-        <v>3791</v>
+        <v>3802</v>
       </c>
       <c r="H15" t="n">
-        <v>-4548.6242</v>
+        <v>-4549.2453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.070023</v>
+        <v>-0.069837</v>
       </c>
       <c r="J15" t="n">
         <v>20</v>
@@ -940,7 +940,7 @@
         <v>44538</v>
       </c>
       <c r="C16" t="n">
-        <v>16.625</v>
+        <v>16.6233</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>44547</v>
@@ -949,16 +949,16 @@
         <v>44546</v>
       </c>
       <c r="F16" t="n">
-        <v>15.4854</v>
+        <v>15.4869</v>
       </c>
       <c r="G16" t="n">
-        <v>3634</v>
+        <v>3645</v>
       </c>
       <c r="H16" t="n">
-        <v>-4176.433</v>
+        <v>-4177.3707</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.069129</v>
+        <v>-0.068943</v>
       </c>
       <c r="J16" t="n">
         <v>8</v>
@@ -972,7 +972,7 @@
         <v>44585</v>
       </c>
       <c r="C17" t="n">
-        <v>14.7744</v>
+        <v>14.773</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>44599</v>
@@ -981,16 +981,16 @@
         <v>44589</v>
       </c>
       <c r="F17" t="n">
-        <v>14.3057</v>
+        <v>14.3071</v>
       </c>
       <c r="G17" t="n">
-        <v>3807</v>
+        <v>3819</v>
       </c>
       <c r="H17" t="n">
-        <v>-1817.6447</v>
+        <v>-1812.2684</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.032316</v>
+        <v>-0.032122</v>
       </c>
       <c r="J17" t="n">
         <v>13</v>
@@ -1004,7 +1004,7 @@
         <v>44603</v>
       </c>
       <c r="C18" t="n">
-        <v>14.5043</v>
+        <v>14.5029</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>44609</v>
@@ -1013,16 +1013,16 @@
         <v>44608</v>
       </c>
       <c r="F18" t="n">
-        <v>14.3357</v>
+        <v>14.3371</v>
       </c>
       <c r="G18" t="n">
-        <v>3753</v>
+        <v>3765</v>
       </c>
       <c r="H18" t="n">
-        <v>-665.422</v>
+        <v>-656.6913</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.012224</v>
+        <v>-0.012027</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
@@ -1036,7 +1036,7 @@
         <v>44644</v>
       </c>
       <c r="C19" t="n">
-        <v>12.9039</v>
+        <v>12.9026</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>44677</v>
@@ -1045,16 +1045,16 @@
         <v>44676</v>
       </c>
       <c r="F19" t="n">
-        <v>12.6462</v>
+        <v>12.6475</v>
       </c>
       <c r="G19" t="n">
-        <v>4167</v>
+        <v>4181</v>
       </c>
       <c r="H19" t="n">
-        <v>-1105.6302</v>
+        <v>-1098.6623</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.020562</v>
+        <v>-0.020366</v>
       </c>
       <c r="J19" t="n">
         <v>32</v>
@@ -1068,7 +1068,7 @@
         <v>44729</v>
       </c>
       <c r="C20" t="n">
-        <v>12.2637</v>
+        <v>12.2625</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>44755</v>
@@ -1077,16 +1077,16 @@
         <v>44754</v>
       </c>
       <c r="F20" t="n">
-        <v>11.8864</v>
+        <v>11.8876</v>
       </c>
       <c r="G20" t="n">
-        <v>4294</v>
+        <v>4310</v>
       </c>
       <c r="H20" t="n">
-        <v>-1651.0002</v>
+        <v>-1646.7433</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.031352</v>
+        <v>-0.031158</v>
       </c>
       <c r="J20" t="n">
         <v>23</v>
@@ -1100,7 +1100,7 @@
         <v>44796</v>
       </c>
       <c r="C21" t="n">
-        <v>10.5532</v>
+        <v>10.5521</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>44827</v>
@@ -1109,16 +1109,16 @@
         <v>44826</v>
       </c>
       <c r="F21" t="n">
-        <v>10.4369</v>
+        <v>10.4379</v>
       </c>
       <c r="G21" t="n">
-        <v>4834</v>
+        <v>4852</v>
       </c>
       <c r="H21" t="n">
-        <v>-592.6194</v>
+        <v>-584.6418</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.011617</v>
+        <v>-0.011419</v>
       </c>
       <c r="J21" t="n">
         <v>30</v>
@@ -1132,7 +1132,7 @@
         <v>44876</v>
       </c>
       <c r="C22" t="n">
-        <v>10.103</v>
+        <v>10.102</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>44918</v>
@@ -1141,16 +1141,16 @@
         <v>44917</v>
       </c>
       <c r="F22" t="n">
-        <v>11.1267</v>
+        <v>11.1278</v>
       </c>
       <c r="G22" t="n">
-        <v>4990</v>
+        <v>5011</v>
       </c>
       <c r="H22" t="n">
-        <v>5076.1378</v>
+        <v>5108.1385</v>
       </c>
       <c r="I22" t="n">
-        <v>0.100689</v>
+        <v>0.100909</v>
       </c>
       <c r="J22" t="n">
         <v>39</v>
@@ -1164,7 +1164,7 @@
         <v>44929</v>
       </c>
       <c r="C23" t="n">
-        <v>12.4737</v>
+        <v>12.4725</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>44964</v>
@@ -1173,16 +1173,16 @@
         <v>44963</v>
       </c>
       <c r="F23" t="n">
-        <v>12.3563</v>
+        <v>12.3575</v>
       </c>
       <c r="G23" t="n">
-        <v>4449</v>
+        <v>4468</v>
       </c>
       <c r="H23" t="n">
-        <v>-555.6712</v>
+        <v>-546.9502</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.010013</v>
+        <v>-0.009815000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>34</v>
@@ -1196,7 +1196,7 @@
         <v>44988</v>
       </c>
       <c r="C24" t="n">
-        <v>12.0036</v>
+        <v>12.0024</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>44995</v>
@@ -1205,16 +1205,16 @@
         <v>44994</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2866</v>
+        <v>11.2877</v>
       </c>
       <c r="G24" t="n">
-        <v>4577</v>
+        <v>4597</v>
       </c>
       <c r="H24" t="n">
-        <v>-3313.6293</v>
+        <v>-3317.4023</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.060313</v>
+        <v>-0.060125</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -1228,7 +1228,7 @@
         <v>45034</v>
       </c>
       <c r="C25" t="n">
-        <v>11.0033</v>
+        <v>11.0022</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>45042</v>
@@ -1237,16 +1237,16 @@
         <v>45041</v>
       </c>
       <c r="F25" t="n">
-        <v>10.2669</v>
+        <v>10.2679</v>
       </c>
       <c r="G25" t="n">
-        <v>4692</v>
+        <v>4714</v>
       </c>
       <c r="H25" t="n">
-        <v>-3485.0396</v>
+        <v>-3491.3536</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.06750399999999999</v>
+        <v>-0.067317</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
@@ -1260,7 +1260,7 @@
         <v>45054</v>
       </c>
       <c r="C26" t="n">
-        <v>11.3134</v>
+        <v>11.3123</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>45064</v>
@@ -1269,16 +1269,16 @@
         <v>45063</v>
       </c>
       <c r="F26" t="n">
-        <v>10.6368</v>
+        <v>10.6379</v>
       </c>
       <c r="G26" t="n">
-        <v>4255</v>
+        <v>4276</v>
       </c>
       <c r="H26" t="n">
-        <v>-2906.8886</v>
+        <v>-2911.8493</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.060386</v>
+        <v>-0.060198</v>
       </c>
       <c r="J26" t="n">
         <v>9</v>
@@ -1292,7 +1292,7 @@
         <v>45124</v>
       </c>
       <c r="C27" t="n">
-        <v>9.6929</v>
+        <v>9.6919</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>45132</v>
@@ -1301,16 +1301,16 @@
         <v>45131</v>
       </c>
       <c r="F27" t="n">
-        <v>10.157</v>
+        <v>10.158</v>
       </c>
       <c r="G27" t="n">
-        <v>4667</v>
+        <v>4690</v>
       </c>
       <c r="H27" t="n">
-        <v>2137.9062</v>
+        <v>2157.7519</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04726</v>
+        <v>0.04747</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
@@ -1324,7 +1324,7 @@
         <v>45132</v>
       </c>
       <c r="C28" t="n">
-        <v>10.113</v>
+        <v>10.112</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>45155</v>
@@ -1333,16 +1333,16 @@
         <v>45154</v>
       </c>
       <c r="F28" t="n">
-        <v>10.007</v>
+        <v>10.008</v>
       </c>
       <c r="G28" t="n">
-        <v>4684</v>
+        <v>4709</v>
       </c>
       <c r="H28" t="n">
-        <v>-524.9453</v>
+        <v>-518.2726</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.011082</v>
+        <v>-0.010884</v>
       </c>
       <c r="J28" t="n">
         <v>22</v>
@@ -1356,7 +1356,7 @@
         <v>45294</v>
       </c>
       <c r="C29" t="n">
-        <v>7.5523</v>
+        <v>7.5515</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>45300</v>
@@ -1365,16 +1365,16 @@
         <v>45299</v>
       </c>
       <c r="F29" t="n">
-        <v>7.6177</v>
+        <v>7.6185</v>
       </c>
       <c r="G29" t="n">
-        <v>6203</v>
+        <v>6237</v>
       </c>
       <c r="H29" t="n">
-        <v>377.7503</v>
+        <v>389.2824</v>
       </c>
       <c r="I29" t="n">
-        <v>0.008064</v>
+        <v>0.008265</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -1388,7 +1388,7 @@
         <v>45307</v>
       </c>
       <c r="C30" t="n">
-        <v>7.6723</v>
+        <v>7.6715</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>45315</v>
@@ -1397,16 +1397,16 @@
         <v>45314</v>
       </c>
       <c r="F30" t="n">
-        <v>7.7677</v>
+        <v>7.7684</v>
       </c>
       <c r="G30" t="n">
-        <v>6155</v>
+        <v>6190</v>
       </c>
       <c r="H30" t="n">
-        <v>558.4801</v>
+        <v>571.2132</v>
       </c>
       <c r="I30" t="n">
-        <v>0.011826</v>
+        <v>0.012029</v>
       </c>
       <c r="J30" t="n">
         <v>7</v>
@@ -1420,7 +1420,7 @@
         <v>45316</v>
       </c>
       <c r="C31" t="n">
-        <v>8.0624</v>
+        <v>8.0616</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>45366</v>
@@ -1429,16 +1429,16 @@
         <v>45365</v>
       </c>
       <c r="F31" t="n">
-        <v>9.0373</v>
+        <v>9.0382</v>
       </c>
       <c r="G31" t="n">
-        <v>5927</v>
+        <v>5961</v>
       </c>
       <c r="H31" t="n">
-        <v>5747.6495</v>
+        <v>5790.8138</v>
       </c>
       <c r="I31" t="n">
-        <v>0.120279</v>
+        <v>0.120503</v>
       </c>
       <c r="J31" t="n">
         <v>49</v>
@@ -1452,7 +1452,7 @@
         <v>45372</v>
       </c>
       <c r="C32" t="n">
-        <v>8.8026</v>
+        <v>8.8018</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>45377</v>
@@ -1461,16 +1461,16 @@
         <v>45376</v>
       </c>
       <c r="F32" t="n">
-        <v>9.0373</v>
+        <v>9.0382</v>
       </c>
       <c r="G32" t="n">
-        <v>6081</v>
+        <v>6118</v>
       </c>
       <c r="H32" t="n">
-        <v>1394.3491</v>
+        <v>1413.7475</v>
       </c>
       <c r="I32" t="n">
-        <v>0.026049</v>
+        <v>0.026254</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
@@ -1484,7 +1484,7 @@
         <v>45377</v>
       </c>
       <c r="C33" t="n">
-        <v>8.9727</v>
+        <v>8.9718</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>45393</v>
@@ -1493,16 +1493,16 @@
         <v>45392</v>
       </c>
       <c r="F33" t="n">
-        <v>8.6874</v>
+        <v>8.6883</v>
       </c>
       <c r="G33" t="n">
-        <v>6121</v>
+        <v>6159</v>
       </c>
       <c r="H33" t="n">
-        <v>-1778.7383</v>
+        <v>-1778.9041</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.032387</v>
+        <v>-0.032193</v>
       </c>
       <c r="J33" t="n">
         <v>15</v>
@@ -1516,7 +1516,7 @@
         <v>45401</v>
       </c>
       <c r="C34" t="n">
-        <v>8.9427</v>
+        <v>8.941800000000001</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>45448</v>
@@ -1525,16 +1525,16 @@
         <v>45447</v>
       </c>
       <c r="F34" t="n">
-        <v>9.3072</v>
+        <v>9.3081</v>
       </c>
       <c r="G34" t="n">
-        <v>5943</v>
+        <v>5981</v>
       </c>
       <c r="H34" t="n">
-        <v>2133.8343</v>
+        <v>2158.3935</v>
       </c>
       <c r="I34" t="n">
-        <v>0.04015</v>
+        <v>0.040358</v>
       </c>
       <c r="J34" t="n">
         <v>44</v>
@@ -1548,7 +1548,7 @@
         <v>45474</v>
       </c>
       <c r="C35" t="n">
-        <v>9.562900000000001</v>
+        <v>9.5619</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>45483</v>
@@ -1557,16 +1557,16 @@
         <v>45482</v>
       </c>
       <c r="F35" t="n">
-        <v>9.2972</v>
+        <v>9.2981</v>
       </c>
       <c r="G35" t="n">
-        <v>5780</v>
+        <v>5819</v>
       </c>
       <c r="H35" t="n">
-        <v>-1568.2066</v>
+        <v>-1567.8133</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.028372</v>
+        <v>-0.028177</v>
       </c>
       <c r="J35" t="n">
         <v>8</v>
@@ -1580,7 +1580,7 @@
         <v>45488</v>
       </c>
       <c r="C36" t="n">
-        <v>9.4628</v>
+        <v>9.4619</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>45499</v>
@@ -1589,16 +1589,16 @@
         <v>45498</v>
       </c>
       <c r="F36" t="n">
-        <v>9.187200000000001</v>
+        <v>9.1882</v>
       </c>
       <c r="G36" t="n">
-        <v>5676</v>
+        <v>5715</v>
       </c>
       <c r="H36" t="n">
-        <v>-1596.0346</v>
+        <v>-1596.3425</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.029715</v>
+        <v>-0.029521</v>
       </c>
       <c r="J36" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>45524</v>
       </c>
       <c r="C37" t="n">
-        <v>9.5129</v>
+        <v>9.511900000000001</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>45539</v>
@@ -1621,16 +1621,16 @@
         <v>45538</v>
       </c>
       <c r="F37" t="n">
-        <v>9.177199999999999</v>
+        <v>9.1782</v>
       </c>
       <c r="G37" t="n">
-        <v>5478</v>
+        <v>5517</v>
       </c>
       <c r="H37" t="n">
-        <v>-1869.1705</v>
+        <v>-1872.1665</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.035869</v>
+        <v>-0.035676</v>
       </c>
       <c r="J37" t="n">
         <v>14</v>
@@ -1644,7 +1644,7 @@
         <v>45560</v>
       </c>
       <c r="C38" t="n">
-        <v>10.3131</v>
+        <v>10.3121</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>45595</v>
@@ -1653,16 +1653,16 @@
         <v>45594</v>
       </c>
       <c r="F38" t="n">
-        <v>10.7168</v>
+        <v>10.7179</v>
       </c>
       <c r="G38" t="n">
-        <v>4872</v>
+        <v>4907</v>
       </c>
       <c r="H38" t="n">
-        <v>1936.0453</v>
+        <v>1960.273</v>
       </c>
       <c r="I38" t="n">
-        <v>0.038532</v>
+        <v>0.03874</v>
       </c>
       <c r="J38" t="n">
         <v>34</v>
@@ -1676,7 +1676,7 @@
         <v>45609</v>
       </c>
       <c r="C39" t="n">
-        <v>10.9433</v>
+        <v>10.9422</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>45611</v>
@@ -1685,16 +1685,16 @@
         <v>45610</v>
       </c>
       <c r="F39" t="n">
-        <v>10.8367</v>
+        <v>10.8378</v>
       </c>
       <c r="G39" t="n">
-        <v>4768</v>
+        <v>4804</v>
       </c>
       <c r="H39" t="n">
-        <v>-539.1083</v>
+        <v>-532.7156</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.010332</v>
+        <v>-0.010134</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -1708,7 +1708,7 @@
         <v>45616</v>
       </c>
       <c r="C40" t="n">
-        <v>10.9933</v>
+        <v>10.9922</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>45622</v>
@@ -1717,16 +1717,16 @@
         <v>45621</v>
       </c>
       <c r="F40" t="n">
-        <v>10.6668</v>
+        <v>10.6679</v>
       </c>
       <c r="G40" t="n">
-        <v>4698</v>
+        <v>4733</v>
       </c>
       <c r="H40" t="n">
-        <v>-1564.4153</v>
+        <v>-1565.8185</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.030291</v>
+        <v>-0.030097</v>
       </c>
       <c r="J40" t="n">
         <v>5</v>
@@ -1740,182 +1740,22 @@
         <v>45632</v>
       </c>
       <c r="C41" t="n">
-        <v>11.0733</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>45663</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>45660</v>
-      </c>
-      <c r="F41" t="n">
-        <v>10.8367</v>
-      </c>
+        <v>11.0722</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>4522</v>
+        <v>4558</v>
       </c>
       <c r="H41" t="n">
-        <v>-1099.5063</v>
+        <v>111.5084</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.021958</v>
+        <v>0.00221</v>
       </c>
       <c r="J41" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45698</v>
-      </c>
-      <c r="C42" t="n">
-        <v>10.8232</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>45720</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>45719</v>
-      </c>
-      <c r="F42" t="n">
-        <v>10.9067</v>
-      </c>
-      <c r="G42" t="n">
-        <v>4525</v>
-      </c>
-      <c r="H42" t="n">
-        <v>348.2531</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.007111</v>
-      </c>
-      <c r="J42" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45721</v>
-      </c>
-      <c r="C43" t="n">
-        <v>11.0333</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>45737</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>45736</v>
-      </c>
-      <c r="F43" t="n">
-        <v>10.8168</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4471</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-997.5249</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-0.020221</v>
-      </c>
-      <c r="J43" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>45785</v>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>45784</v>
-      </c>
-      <c r="C44" t="n">
-        <v>10.4831</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>45862</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>45861</v>
-      </c>
-      <c r="F44" t="n">
-        <v>12.1064</v>
-      </c>
-      <c r="G44" t="n">
-        <v>4610</v>
-      </c>
-      <c r="H44" t="n">
-        <v>7451.8167</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.154195</v>
-      </c>
-      <c r="J44" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="C45" t="n">
-        <v>11.4034</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="F45" t="n">
-        <v>11.4866</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4891</v>
-      </c>
-      <c r="H45" t="n">
-        <v>373.017</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.006688</v>
-      </c>
-      <c r="J45" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>46013</v>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="C46" t="n">
-        <v>11.5235</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>4873</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-569.7172</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-0.010146</v>
-      </c>
-      <c r="J46" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
